--- a/WorkBot/refactor-experimental/data/orders/Paper Rolls .com/Paper Rolls .com_Bakery_20251111.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Paper Rolls .com/Paper Rolls .com_Bakery_20251111.xlsx
@@ -450,20 +450,14 @@
           <t>Register Tape - Paper (3" x 165')</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>42.00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>168.00</t>
-        </is>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>42</v>
+      </c>
+      <c r="E2" t="n">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
